--- a/outputs/Intermittent/Intermittent - High N_d_report.xlsx
+++ b/outputs/Intermittent/Intermittent - High N_d_report.xlsx
@@ -511,13 +511,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.039675925925926</v>
+        <v>2.549537037037037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8495014878019801</v>
+        <v>1.596726976360404</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06382978226673673</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9052607539863659</v>
+        <v>6.271759259259259</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6657104369511285</v>
+        <v>2.504348070708075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.280970832355533</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04162762763550344</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.274348541008814</v>
+        <v>6.271759259259259</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7354672554276577</v>
+        <v>2.504348070708075</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.774696247688219</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0880281690140845</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9662436424100156</v>
+        <v>6.271759259259259</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6562480316356974</v>
+        <v>2.504348070708075</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.14654594232059</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.07922535211267605</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9154526115023474</v>
+        <v>6.271759259259259</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6548441929638364</v>
+        <v>2.504348070708075</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1681086519114691</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007926092937685291</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.727449280400448</v>
+        <v>6.271759259259259</v>
       </c>
       <c r="E9" t="n">
-        <v>1.022778724611711</v>
+        <v>2.504348070708075</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.968295628249261</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="10">
@@ -703,13 +703,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.023194444444445</v>
+        <v>1.815277777777778</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8245116399690452</v>
+        <v>1.347322447589209</v>
       </c>
       <c r="F12" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1874999959990281</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8102140259926172</v>
+        <v>2.023611111111111</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6433247737380539</v>
+        <v>1.422536857558043</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5538808989584132</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1749996557049325</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.264945259488742</v>
+        <v>2.023611111111111</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8707459435910856</v>
+        <v>1.422536857558043</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.857774748313371</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2232142857142857</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7989734299516909</v>
+        <v>2.023611111111111</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6178152537819726</v>
+        <v>1.422536857558043</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4143633540372669</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2008928571428572</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7649094202898551</v>
+        <v>2.023611111111111</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6157147606992163</v>
+        <v>1.422536857558043</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6729270186335403</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2013737779200001</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.344597988977778</v>
+        <v>2.023611111111111</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9399525463371636</v>
+        <v>1.422536857558043</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.194504888320002</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="18">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>1.55884572681199</v>
+        <v>1.732050807568877</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9999999629627205</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.166674038749539</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1.040832964989</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4999888467824271</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.499999927522425</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.277777733738201</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1.696947100181412</v>
+        <v>1.414213562373095</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.166666660920772</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6097560975609756</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.072719060523939</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7660437811538432</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1.334688346883469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5487804878048781</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.065447154471545</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.754095500447629</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1.501219512195122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
